--- a/artfynd/A 5732-2025 artfynd.xlsx
+++ b/artfynd/A 5732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>100226701</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650523.510656266</v>
+        <v>650524</v>
       </c>
       <c r="R2" t="n">
-        <v>6644889.947173863</v>
+        <v>6644890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +751,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -815,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100226882</v>
+        <v>100226799</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -859,14 +839,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hakriset, 400 m S om, Upl</t>
+          <t>Hakriset, 250 m S om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650485.2140934077</v>
+        <v>650540</v>
       </c>
       <c r="R3" t="n">
-        <v>6644718.687527693</v>
+        <v>6644839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,19 +876,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,6 +896,11 @@
           <t>Lövskog på blockmark</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lind och ek på bergsluttning med flyttblock</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
           <t>Sten/berg på land</t>
@@ -948,6 +923,279 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100226882</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hakriset, 400 m S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>650485</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6644719</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lövskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stone/rock on land # Flyttblock</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100227081</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hakriset 420 m S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>650438</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6644703</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Beteshage med stora ekar och hassel</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Död hasselstam i hasselbukett</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Corylus avellana # Död hasselstam i hasselbukett</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
